--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G14" s="41" t="n"/>
       <c r="H14" s="26">
-        <f>H29*0.5</f>
+        <f>H30*0.5</f>
         <v/>
       </c>
       <c r="I14" s="27" t="n"/>
@@ -2578,25 +2578,19 @@
           <t>Cantidad de Trabajadores ch gral</t>
         </is>
       </c>
-      <c r="J29" s="34" t="n">
-        <v>479</v>
-      </c>
+      <c r="J29" s="34" t="n"/>
       <c r="K29" s="31" t="inlineStr">
         <is>
           <t>Cantidad de Trabajadores</t>
         </is>
       </c>
-      <c r="L29" s="34" t="n">
-        <v>5255</v>
-      </c>
+      <c r="L29" s="34" t="n"/>
       <c r="M29" s="31" t="inlineStr">
         <is>
           <t>Cantidad de Trabajadores</t>
         </is>
       </c>
-      <c r="N29" s="38" t="n">
-        <v>4851</v>
-      </c>
+      <c r="N29" s="38" t="n"/>
       <c r="O29" s="69" t="n"/>
     </row>
     <row r="30" customFormat="1" s="52">
@@ -2613,25 +2607,19 @@
           <t>cantidad trab. Ch. integral</t>
         </is>
       </c>
-      <c r="J30" s="52" t="n">
-        <v>123</v>
-      </c>
+      <c r="J30" s="52" t="n"/>
       <c r="K30" s="52" t="inlineStr">
         <is>
           <t>cantidad trab. Ch. integral</t>
         </is>
       </c>
-      <c r="L30" s="69" t="n">
-        <v>373</v>
-      </c>
+      <c r="L30" s="69" t="n"/>
       <c r="M30" s="52" t="inlineStr">
         <is>
           <t>cantidad trab. Ch. integral</t>
         </is>
       </c>
-      <c r="N30" s="69" t="n">
-        <v>784</v>
-      </c>
+      <c r="N30" s="69" t="n"/>
       <c r="O30" s="69" t="n"/>
     </row>
     <row r="31" customFormat="1" s="52">

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -1717,7 +1717,7 @@
         <v/>
       </c>
       <c r="O11" s="19">
-        <f>SUM(G11,I11,#REF!,M11)</f>
+        <f>SUM(G11,I11,K11,M11)</f>
         <v/>
       </c>
       <c r="P11" s="112">
@@ -1762,7 +1762,7 @@
         <v/>
       </c>
       <c r="O12" s="19">
-        <f>SUM(G12,I12,K11,M12)</f>
+        <f>SUM(G12,I12,K12,M12)</f>
         <v/>
       </c>
       <c r="P12" s="112">

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -1376,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Z36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
     <col width="3.59765625" customWidth="1" style="69" min="1" max="1"/>
@@ -2626,7 +2626,7 @@
       <c r="A31" s="69" t="n"/>
       <c r="B31" s="52" t="inlineStr">
         <is>
-          <t>CHPS — Comité Paritario de Higiene y Seguridad</t>
+          <t>CPHS — Comité Paritario de Higiene y Seguridad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -1053,6 +1053,36 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1376,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A2:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
     <col width="3.59765625" customWidth="1" style="69" min="1" max="1"/>
@@ -1409,9 +1439,7 @@
   <sheetData>
     <row r="1" ht="14.4" customHeight="1" thickBot="1"/>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="B2" s="93" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="B2" s="93" t="n"/>
       <c r="C2" s="94" t="n"/>
       <c r="D2" s="94" t="n"/>
       <c r="E2" s="95" t="inlineStr">
@@ -2216,13 +2244,17 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G22" s="41" t="n"/>
+      <c r="G22" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I22" s="27" t="n"/>
+      <c r="I22" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2420,13 +2452,17 @@
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G26" s="44" t="n"/>
+      <c r="G26" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I26" s="28" t="n"/>
+      <c r="I26" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2698,5 +2734,6 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" scale="70"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -1060,11 +1060,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>95250</colOff>
       <row>1</row>
-      <rowOff>0</rowOff>
+      <rowOff>123825</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="18" customFormat="1" s="52">
       <c r="A18" s="69" t="n"/>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>N° de Inspecciones a bodegas SUSPEL/RESPEL</t>
         </is>

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -185,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -728,6 +728,7 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -736,7 +737,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1042,6 +1043,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,6 +1086,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1406,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Z36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
     <col width="3.59765625" customWidth="1" style="69" min="1" max="1"/>
@@ -1437,7 +1448,18 @@
     <col width="11.3984375" customWidth="1" style="36" min="27" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1" thickBot="1"/>
+    <row r="1" ht="14.4" customHeight="1" thickBot="1">
+      <c r="Q1" s="117" t="n"/>
+      <c r="R1" s="117" t="n"/>
+      <c r="S1" s="117" t="n"/>
+      <c r="T1" s="117" t="n"/>
+      <c r="U1" s="117" t="n"/>
+      <c r="V1" s="117" t="n"/>
+      <c r="W1" s="117" t="n"/>
+      <c r="X1" s="117" t="n"/>
+      <c r="Y1" s="117" t="n"/>
+      <c r="Z1" s="117" t="n"/>
+    </row>
     <row r="2" ht="21.75" customHeight="1">
       <c r="B2" s="93" t="n"/>
       <c r="C2" s="94" t="n"/>
@@ -1459,27 +1481,47 @@
       <c r="M2" s="94" t="n"/>
       <c r="N2" s="94" t="n"/>
       <c r="O2" s="94" t="n"/>
-      <c r="P2" s="94" t="n"/>
-      <c r="Q2" s="94" t="n"/>
-      <c r="R2" s="94" t="n"/>
-      <c r="S2" s="94" t="n"/>
-      <c r="T2" s="94" t="n"/>
-      <c r="U2" s="94" t="n"/>
-      <c r="V2" s="94" t="n"/>
-      <c r="W2" s="94" t="n"/>
-      <c r="X2" s="94" t="n"/>
-      <c r="Y2" s="94" t="n"/>
-      <c r="Z2" s="96" t="n"/>
+      <c r="P2" s="96" t="n"/>
+      <c r="Q2" s="117" t="n"/>
+      <c r="R2" s="117" t="n"/>
+      <c r="S2" s="117" t="n"/>
+      <c r="T2" s="117" t="n"/>
+      <c r="U2" s="117" t="n"/>
+      <c r="V2" s="117" t="n"/>
+      <c r="W2" s="117" t="n"/>
+      <c r="X2" s="117" t="n"/>
+      <c r="Y2" s="117" t="n"/>
+      <c r="Z2" s="117" t="n"/>
     </row>
     <row r="3" ht="21.75" customHeight="1">
       <c r="B3" s="97" t="n"/>
       <c r="E3" s="97" t="n"/>
-      <c r="Z3" s="98" t="n"/>
+      <c r="P3" s="98" t="n"/>
+      <c r="Q3" s="117" t="n"/>
+      <c r="R3" s="117" t="n"/>
+      <c r="S3" s="117" t="n"/>
+      <c r="T3" s="117" t="n"/>
+      <c r="U3" s="117" t="n"/>
+      <c r="V3" s="117" t="n"/>
+      <c r="W3" s="117" t="n"/>
+      <c r="X3" s="117" t="n"/>
+      <c r="Y3" s="117" t="n"/>
+      <c r="Z3" s="117" t="n"/>
     </row>
     <row r="4" ht="21.75" customHeight="1">
       <c r="B4" s="97" t="n"/>
       <c r="E4" s="97" t="n"/>
-      <c r="Z4" s="98" t="n"/>
+      <c r="P4" s="98" t="n"/>
+      <c r="Q4" s="117" t="n"/>
+      <c r="R4" s="117" t="n"/>
+      <c r="S4" s="117" t="n"/>
+      <c r="T4" s="117" t="n"/>
+      <c r="U4" s="117" t="n"/>
+      <c r="V4" s="117" t="n"/>
+      <c r="W4" s="117" t="n"/>
+      <c r="X4" s="117" t="n"/>
+      <c r="Y4" s="117" t="n"/>
+      <c r="Z4" s="117" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" thickBot="1">
       <c r="B5" s="99" t="n"/>
@@ -1496,17 +1538,17 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="100" t="n"/>
       <c r="O5" s="100" t="n"/>
-      <c r="P5" s="100" t="n"/>
-      <c r="Q5" s="100" t="n"/>
-      <c r="R5" s="100" t="n"/>
-      <c r="S5" s="100" t="n"/>
-      <c r="T5" s="100" t="n"/>
-      <c r="U5" s="100" t="n"/>
-      <c r="V5" s="100" t="n"/>
-      <c r="W5" s="100" t="n"/>
-      <c r="X5" s="100" t="n"/>
-      <c r="Y5" s="100" t="n"/>
-      <c r="Z5" s="101" t="n"/>
+      <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="117" t="n"/>
+      <c r="R5" s="117" t="n"/>
+      <c r="S5" s="117" t="n"/>
+      <c r="T5" s="117" t="n"/>
+      <c r="U5" s="117" t="n"/>
+      <c r="V5" s="117" t="n"/>
+      <c r="W5" s="117" t="n"/>
+      <c r="X5" s="117" t="n"/>
+      <c r="Y5" s="117" t="n"/>
+      <c r="Z5" s="117" t="n"/>
     </row>
     <row r="6" ht="14.7" customHeight="1">
       <c r="B6" s="102" t="inlineStr">
@@ -1527,17 +1569,17 @@
       <c r="M6" s="94" t="n"/>
       <c r="N6" s="94" t="n"/>
       <c r="O6" s="94" t="n"/>
-      <c r="P6" s="94" t="n"/>
-      <c r="Q6" s="94" t="n"/>
-      <c r="R6" s="94" t="n"/>
-      <c r="S6" s="94" t="n"/>
-      <c r="T6" s="103" t="n"/>
-      <c r="U6" s="36" t="n"/>
-      <c r="V6" s="36" t="n"/>
-      <c r="W6" s="36" t="n"/>
-      <c r="X6" s="36" t="n"/>
-      <c r="Y6" s="36" t="n"/>
-      <c r="Z6" s="37" t="n"/>
+      <c r="P6" s="103" t="n"/>
+      <c r="Q6" s="117" t="n"/>
+      <c r="R6" s="117" t="n"/>
+      <c r="S6" s="117" t="n"/>
+      <c r="T6" s="117" t="n"/>
+      <c r="U6" s="118" t="n"/>
+      <c r="V6" s="118" t="n"/>
+      <c r="W6" s="118" t="n"/>
+      <c r="X6" s="118" t="n"/>
+      <c r="Y6" s="118" t="n"/>
+      <c r="Z6" s="118" t="n"/>
     </row>
     <row r="7" ht="14.7" customHeight="1" thickBot="1">
       <c r="B7" s="99" t="n"/>
@@ -1554,17 +1596,17 @@
       <c r="M7" s="100" t="n"/>
       <c r="N7" s="100" t="n"/>
       <c r="O7" s="100" t="n"/>
-      <c r="P7" s="100" t="n"/>
-      <c r="Q7" s="100" t="n"/>
-      <c r="R7" s="100" t="n"/>
-      <c r="S7" s="100" t="n"/>
-      <c r="T7" s="104" t="n"/>
-      <c r="U7" s="36" t="n"/>
-      <c r="V7" s="36" t="n"/>
-      <c r="W7" s="36" t="n"/>
-      <c r="X7" s="36" t="n"/>
-      <c r="Y7" s="36" t="n"/>
-      <c r="Z7" s="37" t="n"/>
+      <c r="P7" s="104" t="n"/>
+      <c r="Q7" s="117" t="n"/>
+      <c r="R7" s="117" t="n"/>
+      <c r="S7" s="117" t="n"/>
+      <c r="T7" s="117" t="n"/>
+      <c r="U7" s="118" t="n"/>
+      <c r="V7" s="118" t="n"/>
+      <c r="W7" s="118" t="n"/>
+      <c r="X7" s="118" t="n"/>
+      <c r="Y7" s="118" t="n"/>
+      <c r="Z7" s="118" t="n"/>
     </row>
     <row r="8" ht="14.4" customHeight="1" thickBot="1">
       <c r="B8" s="66" t="n"/>
@@ -1582,11 +1624,16 @@
       <c r="N8" s="94" t="n"/>
       <c r="O8" s="94" t="n"/>
       <c r="P8" s="94" t="n"/>
-      <c r="Q8" s="94" t="n"/>
-      <c r="R8" s="94" t="n"/>
-      <c r="S8" s="94" t="n"/>
-      <c r="T8" s="94" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Q8" s="117" t="n"/>
+      <c r="R8" s="117" t="n"/>
+      <c r="S8" s="117" t="n"/>
+      <c r="T8" s="117" t="n"/>
+      <c r="U8" s="117" t="n"/>
+      <c r="V8" s="117" t="n"/>
+      <c r="W8" s="117" t="n"/>
+      <c r="X8" s="117" t="n"/>
+      <c r="Y8" s="117" t="n"/>
+      <c r="Z8" s="118" t="n"/>
     </row>
     <row r="9" ht="28.2" customHeight="1" thickBot="1">
       <c r="B9" s="90" t="inlineStr">
@@ -1662,7 +1709,16 @@
 HH Capacitación</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="n"/>
+      <c r="Q9" s="117" t="n"/>
+      <c r="R9" s="117" t="n"/>
+      <c r="S9" s="117" t="n"/>
+      <c r="T9" s="117" t="n"/>
+      <c r="U9" s="117" t="n"/>
+      <c r="V9" s="117" t="n"/>
+      <c r="W9" s="117" t="n"/>
+      <c r="X9" s="117" t="n"/>
+      <c r="Y9" s="117" t="n"/>
+      <c r="Z9" s="118" t="n"/>
     </row>
     <row r="10" customFormat="1" s="52">
       <c r="A10" s="69" t="n"/>
@@ -1707,7 +1763,16 @@
         <f>SUM(N10,L10,J10,H10)</f>
         <v/>
       </c>
-      <c r="Z10" s="14" t="n"/>
+      <c r="Q10" s="117" t="n"/>
+      <c r="R10" s="117" t="n"/>
+      <c r="S10" s="117" t="n"/>
+      <c r="T10" s="117" t="n"/>
+      <c r="U10" s="117" t="n"/>
+      <c r="V10" s="117" t="n"/>
+      <c r="W10" s="117" t="n"/>
+      <c r="X10" s="117" t="n"/>
+      <c r="Y10" s="117" t="n"/>
+      <c r="Z10" s="119" t="n"/>
     </row>
     <row r="11" customFormat="1" s="52">
       <c r="A11" s="69" t="n"/>
@@ -1752,7 +1817,16 @@
         <f>SUM(N11,L11,J11,H11)</f>
         <v/>
       </c>
-      <c r="Z11" s="14" t="n"/>
+      <c r="Q11" s="117" t="n"/>
+      <c r="R11" s="117" t="n"/>
+      <c r="S11" s="117" t="n"/>
+      <c r="T11" s="117" t="n"/>
+      <c r="U11" s="117" t="n"/>
+      <c r="V11" s="117" t="n"/>
+      <c r="W11" s="117" t="n"/>
+      <c r="X11" s="117" t="n"/>
+      <c r="Y11" s="117" t="n"/>
+      <c r="Z11" s="119" t="n"/>
     </row>
     <row r="12" customFormat="1" s="52">
       <c r="A12" s="69" t="n"/>
@@ -1797,7 +1871,16 @@
         <f>SUM(N12,L12,J12,H12)</f>
         <v/>
       </c>
-      <c r="Z12" s="14" t="n"/>
+      <c r="Q12" s="117" t="n"/>
+      <c r="R12" s="117" t="n"/>
+      <c r="S12" s="117" t="n"/>
+      <c r="T12" s="117" t="n"/>
+      <c r="U12" s="117" t="n"/>
+      <c r="V12" s="117" t="n"/>
+      <c r="W12" s="117" t="n"/>
+      <c r="X12" s="117" t="n"/>
+      <c r="Y12" s="117" t="n"/>
+      <c r="Z12" s="119" t="n"/>
     </row>
     <row r="13" customFormat="1" s="52">
       <c r="A13" s="69" t="n"/>
@@ -1842,7 +1925,16 @@
         <f>SUM(N13,L13,J13,H13)</f>
         <v/>
       </c>
-      <c r="Z13" s="14" t="n"/>
+      <c r="Q13" s="117" t="n"/>
+      <c r="R13" s="117" t="n"/>
+      <c r="S13" s="117" t="n"/>
+      <c r="T13" s="117" t="n"/>
+      <c r="U13" s="117" t="n"/>
+      <c r="V13" s="117" t="n"/>
+      <c r="W13" s="117" t="n"/>
+      <c r="X13" s="117" t="n"/>
+      <c r="Y13" s="117" t="n"/>
+      <c r="Z13" s="119" t="n"/>
     </row>
     <row r="14" customFormat="1" s="52">
       <c r="A14" s="69" t="n"/>
@@ -1887,7 +1979,16 @@
         <f>SUM(N14,L14,J14,H14)</f>
         <v/>
       </c>
-      <c r="Z14" s="14" t="n"/>
+      <c r="Q14" s="117" t="n"/>
+      <c r="R14" s="117" t="n"/>
+      <c r="S14" s="117" t="n"/>
+      <c r="T14" s="117" t="n"/>
+      <c r="U14" s="117" t="n"/>
+      <c r="V14" s="117" t="n"/>
+      <c r="W14" s="117" t="n"/>
+      <c r="X14" s="117" t="n"/>
+      <c r="Y14" s="117" t="n"/>
+      <c r="Z14" s="119" t="n"/>
     </row>
     <row r="15" customFormat="1" s="52">
       <c r="A15" s="69" t="n"/>
@@ -1932,7 +2033,16 @@
         <f>SUM(N15,L15,J15,H15)</f>
         <v/>
       </c>
-      <c r="Z15" s="14" t="n"/>
+      <c r="Q15" s="117" t="n"/>
+      <c r="R15" s="117" t="n"/>
+      <c r="S15" s="117" t="n"/>
+      <c r="T15" s="117" t="n"/>
+      <c r="U15" s="117" t="n"/>
+      <c r="V15" s="117" t="n"/>
+      <c r="W15" s="117" t="n"/>
+      <c r="X15" s="117" t="n"/>
+      <c r="Y15" s="117" t="n"/>
+      <c r="Z15" s="119" t="n"/>
     </row>
     <row r="16" customFormat="1" s="52">
       <c r="A16" s="69" t="n"/>
@@ -1977,7 +2087,16 @@
         <f>SUM(N16,L16,J16,H16)</f>
         <v/>
       </c>
-      <c r="Z16" s="14" t="n"/>
+      <c r="Q16" s="117" t="n"/>
+      <c r="R16" s="117" t="n"/>
+      <c r="S16" s="117" t="n"/>
+      <c r="T16" s="117" t="n"/>
+      <c r="U16" s="117" t="n"/>
+      <c r="V16" s="117" t="n"/>
+      <c r="W16" s="117" t="n"/>
+      <c r="X16" s="117" t="n"/>
+      <c r="Y16" s="117" t="n"/>
+      <c r="Z16" s="119" t="n"/>
     </row>
     <row r="17" customFormat="1" s="52">
       <c r="A17" s="69" t="n"/>
@@ -2027,7 +2146,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z17" s="14" t="n"/>
+      <c r="Q17" s="117" t="n"/>
+      <c r="R17" s="117" t="n"/>
+      <c r="S17" s="117" t="n"/>
+      <c r="T17" s="117" t="n"/>
+      <c r="U17" s="117" t="n"/>
+      <c r="V17" s="117" t="n"/>
+      <c r="W17" s="117" t="n"/>
+      <c r="X17" s="117" t="n"/>
+      <c r="Y17" s="117" t="n"/>
+      <c r="Z17" s="119" t="n"/>
     </row>
     <row r="18" customFormat="1" s="52">
       <c r="A18" s="69" t="n"/>
@@ -2077,7 +2205,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z18" s="14" t="n"/>
+      <c r="Q18" s="117" t="n"/>
+      <c r="R18" s="117" t="n"/>
+      <c r="S18" s="117" t="n"/>
+      <c r="T18" s="117" t="n"/>
+      <c r="U18" s="117" t="n"/>
+      <c r="V18" s="117" t="n"/>
+      <c r="W18" s="117" t="n"/>
+      <c r="X18" s="117" t="n"/>
+      <c r="Y18" s="117" t="n"/>
+      <c r="Z18" s="119" t="n"/>
     </row>
     <row r="19" customFormat="1" s="52">
       <c r="A19" s="69" t="n"/>
@@ -2127,7 +2264,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z19" s="14" t="n"/>
+      <c r="Q19" s="117" t="n"/>
+      <c r="R19" s="117" t="n"/>
+      <c r="S19" s="117" t="n"/>
+      <c r="T19" s="117" t="n"/>
+      <c r="U19" s="117" t="n"/>
+      <c r="V19" s="117" t="n"/>
+      <c r="W19" s="117" t="n"/>
+      <c r="X19" s="117" t="n"/>
+      <c r="Y19" s="117" t="n"/>
+      <c r="Z19" s="119" t="n"/>
     </row>
     <row r="20" customFormat="1" s="52">
       <c r="A20" s="69" t="n"/>
@@ -2177,7 +2323,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z20" s="14" t="n"/>
+      <c r="Q20" s="117" t="n"/>
+      <c r="R20" s="117" t="n"/>
+      <c r="S20" s="117" t="n"/>
+      <c r="T20" s="117" t="n"/>
+      <c r="U20" s="117" t="n"/>
+      <c r="V20" s="117" t="n"/>
+      <c r="W20" s="117" t="n"/>
+      <c r="X20" s="117" t="n"/>
+      <c r="Y20" s="117" t="n"/>
+      <c r="Z20" s="119" t="n"/>
     </row>
     <row r="21" customFormat="1" s="52">
       <c r="A21" s="69" t="n"/>
@@ -2227,7 +2382,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z21" s="14" t="n"/>
+      <c r="Q21" s="117" t="n"/>
+      <c r="R21" s="117" t="n"/>
+      <c r="S21" s="117" t="n"/>
+      <c r="T21" s="117" t="n"/>
+      <c r="U21" s="117" t="n"/>
+      <c r="V21" s="117" t="n"/>
+      <c r="W21" s="117" t="n"/>
+      <c r="X21" s="117" t="n"/>
+      <c r="Y21" s="117" t="n"/>
+      <c r="Z21" s="119" t="n"/>
     </row>
     <row r="22" customFormat="1" s="52">
       <c r="A22" s="69" t="n"/>
@@ -2285,7 +2449,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z22" s="14" t="n"/>
+      <c r="Q22" s="117" t="n"/>
+      <c r="R22" s="117" t="n"/>
+      <c r="S22" s="117" t="n"/>
+      <c r="T22" s="117" t="n"/>
+      <c r="U22" s="117" t="n"/>
+      <c r="V22" s="117" t="n"/>
+      <c r="W22" s="117" t="n"/>
+      <c r="X22" s="117" t="n"/>
+      <c r="Y22" s="117" t="n"/>
+      <c r="Z22" s="119" t="n"/>
     </row>
     <row r="23" customFormat="1" s="52">
       <c r="A23" s="69" t="n"/>
@@ -2335,7 +2508,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z23" s="14" t="n"/>
+      <c r="Q23" s="117" t="n"/>
+      <c r="R23" s="117" t="n"/>
+      <c r="S23" s="117" t="n"/>
+      <c r="T23" s="117" t="n"/>
+      <c r="U23" s="117" t="n"/>
+      <c r="V23" s="117" t="n"/>
+      <c r="W23" s="117" t="n"/>
+      <c r="X23" s="117" t="n"/>
+      <c r="Y23" s="117" t="n"/>
+      <c r="Z23" s="119" t="n"/>
     </row>
     <row r="24" customFormat="1" s="52">
       <c r="A24" s="69" t="n"/>
@@ -2385,7 +2567,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z24" s="14" t="n"/>
+      <c r="Q24" s="117" t="n"/>
+      <c r="R24" s="117" t="n"/>
+      <c r="S24" s="117" t="n"/>
+      <c r="T24" s="117" t="n"/>
+      <c r="U24" s="117" t="n"/>
+      <c r="V24" s="117" t="n"/>
+      <c r="W24" s="117" t="n"/>
+      <c r="X24" s="117" t="n"/>
+      <c r="Y24" s="117" t="n"/>
+      <c r="Z24" s="119" t="n"/>
     </row>
     <row r="25" customFormat="1" s="52">
       <c r="A25" s="69" t="n"/>
@@ -2435,7 +2626,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z25" s="14" t="n"/>
+      <c r="Q25" s="117" t="n"/>
+      <c r="R25" s="117" t="n"/>
+      <c r="S25" s="117" t="n"/>
+      <c r="T25" s="117" t="n"/>
+      <c r="U25" s="117" t="n"/>
+      <c r="V25" s="117" t="n"/>
+      <c r="W25" s="117" t="n"/>
+      <c r="X25" s="117" t="n"/>
+      <c r="Y25" s="117" t="n"/>
+      <c r="Z25" s="119" t="n"/>
     </row>
     <row r="26" customFormat="1" s="52">
       <c r="A26" s="69" t="n"/>
@@ -2493,7 +2693,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z26" s="14" t="n"/>
+      <c r="Q26" s="117" t="n"/>
+      <c r="R26" s="117" t="n"/>
+      <c r="S26" s="117" t="n"/>
+      <c r="T26" s="117" t="n"/>
+      <c r="U26" s="117" t="n"/>
+      <c r="V26" s="117" t="n"/>
+      <c r="W26" s="117" t="n"/>
+      <c r="X26" s="117" t="n"/>
+      <c r="Y26" s="117" t="n"/>
+      <c r="Z26" s="119" t="n"/>
     </row>
     <row r="27" customFormat="1" s="52">
       <c r="A27" s="69" t="n"/>
@@ -2543,7 +2752,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z27" s="14" t="n"/>
+      <c r="Q27" s="117" t="n"/>
+      <c r="R27" s="117" t="n"/>
+      <c r="S27" s="117" t="n"/>
+      <c r="T27" s="117" t="n"/>
+      <c r="U27" s="117" t="n"/>
+      <c r="V27" s="117" t="n"/>
+      <c r="W27" s="117" t="n"/>
+      <c r="X27" s="117" t="n"/>
+      <c r="Y27" s="117" t="n"/>
+      <c r="Z27" s="119" t="n"/>
     </row>
     <row r="28" ht="14.4" customFormat="1" customHeight="1" s="52" thickBot="1">
       <c r="A28" s="69" t="n"/>
@@ -2593,7 +2811,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="Z28" s="14" t="n"/>
+      <c r="Q28" s="117" t="n"/>
+      <c r="R28" s="117" t="n"/>
+      <c r="S28" s="117" t="n"/>
+      <c r="T28" s="117" t="n"/>
+      <c r="U28" s="117" t="n"/>
+      <c r="V28" s="117" t="n"/>
+      <c r="W28" s="117" t="n"/>
+      <c r="X28" s="117" t="n"/>
+      <c r="Y28" s="117" t="n"/>
+      <c r="Z28" s="119" t="n"/>
     </row>
     <row r="29" ht="14.4" customFormat="1" customHeight="1" s="52" thickBot="1">
       <c r="A29" s="69" t="n"/>
@@ -2628,6 +2855,16 @@
       </c>
       <c r="N29" s="38" t="n"/>
       <c r="O29" s="69" t="n"/>
+      <c r="Q29" s="117" t="n"/>
+      <c r="R29" s="117" t="n"/>
+      <c r="S29" s="117" t="n"/>
+      <c r="T29" s="117" t="n"/>
+      <c r="U29" s="117" t="n"/>
+      <c r="V29" s="117" t="n"/>
+      <c r="W29" s="117" t="n"/>
+      <c r="X29" s="117" t="n"/>
+      <c r="Y29" s="117" t="n"/>
+      <c r="Z29" s="117" t="n"/>
     </row>
     <row r="30" customFormat="1" s="52">
       <c r="A30" s="69" t="n"/>
@@ -2657,53 +2894,137 @@
       </c>
       <c r="N30" s="69" t="n"/>
       <c r="O30" s="69" t="n"/>
+      <c r="Q30" s="117" t="n"/>
+      <c r="R30" s="117" t="n"/>
+      <c r="S30" s="117" t="n"/>
+      <c r="T30" s="117" t="n"/>
+      <c r="U30" s="117" t="n"/>
+      <c r="V30" s="117" t="n"/>
+      <c r="W30" s="117" t="n"/>
+      <c r="X30" s="117" t="n"/>
+      <c r="Y30" s="117" t="n"/>
+      <c r="Z30" s="117" t="n"/>
     </row>
     <row r="31" customFormat="1" s="52">
       <c r="A31" s="69" t="n"/>
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="53" t="inlineStr">
         <is>
           <t>CPHS — Comité Paritario de Higiene y Seguridad</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="C31" s="120" t="n"/>
+      <c r="D31" s="120" t="n"/>
+      <c r="E31" s="121" t="n"/>
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O31" s="69" t="n"/>
+      <c r="G31" s="45" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="29" t="n"/>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="29" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="23" t="n"/>
+      <c r="P31" s="24" t="n"/>
+      <c r="Q31" s="117" t="n"/>
+      <c r="R31" s="117" t="n"/>
+      <c r="S31" s="117" t="n"/>
+      <c r="T31" s="117" t="n"/>
+      <c r="U31" s="117" t="n"/>
+      <c r="V31" s="117" t="n"/>
+      <c r="W31" s="117" t="n"/>
+      <c r="X31" s="117" t="n"/>
+      <c r="Y31" s="117" t="n"/>
+      <c r="Z31" s="117" t="n"/>
     </row>
     <row r="32" customFormat="1" s="52">
       <c r="A32" s="69" t="n"/>
       <c r="B32" s="52" t="n"/>
       <c r="O32" s="69" t="n"/>
+      <c r="Q32" s="117" t="n"/>
+      <c r="R32" s="117" t="n"/>
+      <c r="S32" s="117" t="n"/>
+      <c r="T32" s="117" t="n"/>
+      <c r="U32" s="117" t="n"/>
+      <c r="V32" s="117" t="n"/>
+      <c r="W32" s="117" t="n"/>
+      <c r="X32" s="117" t="n"/>
+      <c r="Y32" s="117" t="n"/>
+      <c r="Z32" s="117" t="n"/>
     </row>
     <row r="33" customFormat="1" s="52">
       <c r="A33" s="69" t="n"/>
       <c r="B33" s="52" t="n"/>
       <c r="O33" s="69" t="n"/>
+      <c r="Q33" s="117" t="n"/>
+      <c r="R33" s="117" t="n"/>
+      <c r="S33" s="117" t="n"/>
+      <c r="T33" s="117" t="n"/>
+      <c r="U33" s="117" t="n"/>
+      <c r="V33" s="117" t="n"/>
+      <c r="W33" s="117" t="n"/>
+      <c r="X33" s="117" t="n"/>
+      <c r="Y33" s="117" t="n"/>
+      <c r="Z33" s="117" t="n"/>
     </row>
     <row r="34" customFormat="1" s="52">
       <c r="A34" s="69" t="n"/>
       <c r="B34" s="52" t="n"/>
       <c r="O34" s="69" t="n"/>
+      <c r="Q34" s="117" t="n"/>
+      <c r="R34" s="117" t="n"/>
+      <c r="S34" s="117" t="n"/>
+      <c r="T34" s="117" t="n"/>
+      <c r="U34" s="117" t="n"/>
+      <c r="V34" s="117" t="n"/>
+      <c r="W34" s="117" t="n"/>
+      <c r="X34" s="117" t="n"/>
+      <c r="Y34" s="117" t="n"/>
+      <c r="Z34" s="117" t="n"/>
     </row>
     <row r="35" customFormat="1" s="52">
       <c r="A35" s="69" t="n"/>
       <c r="B35" s="52" t="n"/>
       <c r="O35" s="69" t="n"/>
+      <c r="Q35" s="117" t="n"/>
+      <c r="R35" s="117" t="n"/>
+      <c r="S35" s="117" t="n"/>
+      <c r="T35" s="117" t="n"/>
+      <c r="U35" s="117" t="n"/>
+      <c r="V35" s="117" t="n"/>
+      <c r="W35" s="117" t="n"/>
+      <c r="X35" s="117" t="n"/>
+      <c r="Y35" s="117" t="n"/>
+      <c r="Z35" s="117" t="n"/>
     </row>
     <row r="36" customFormat="1" s="52">
       <c r="A36" s="69" t="n"/>
       <c r="B36" s="52" t="n"/>
       <c r="O36" s="69" t="n"/>
+      <c r="Q36" s="117" t="n"/>
+      <c r="R36" s="117" t="n"/>
+      <c r="S36" s="117" t="n"/>
+      <c r="T36" s="117" t="n"/>
+      <c r="U36" s="117" t="n"/>
+      <c r="V36" s="117" t="n"/>
+      <c r="W36" s="117" t="n"/>
+      <c r="X36" s="117" t="n"/>
+      <c r="Y36" s="117" t="n"/>
+      <c r="Z36" s="117" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E2:P5"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B8:P8"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B32:E32"/>
@@ -2717,15 +3038,13 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B2:D5"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B6:T7"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="E2:Z5"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B8:T8"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B6:P7"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B34:E34"/>

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -100,7 +100,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -146,8 +146,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -184,8 +189,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="45">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -729,6 +739,60 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -737,7 +801,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1050,6 +1114,92 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1636,74 +1786,74 @@
       <c r="Z8" s="118" t="n"/>
     </row>
     <row r="9" ht="28.2" customHeight="1" thickBot="1">
-      <c r="B9" s="90" t="inlineStr">
+      <c r="B9" s="122" t="inlineStr">
         <is>
           <t>Cumplimiento Operacional</t>
         </is>
       </c>
-      <c r="C9" s="105" t="n"/>
-      <c r="D9" s="105" t="n"/>
-      <c r="E9" s="106" t="n"/>
-      <c r="F9" s="47" t="inlineStr">
+      <c r="C9" s="123" t="n"/>
+      <c r="D9" s="123" t="n"/>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve">Periodicidad de acuerdo a Plan de Prevención </t>
         </is>
       </c>
-      <c r="G9" s="42" t="inlineStr">
+      <c r="G9" s="125" t="inlineStr">
         <is>
           <t>Cantidad Realizada
 LOS LAGOS</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="125" t="inlineStr">
         <is>
           <t>HH Capacitación 
 LOS LAGOS</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="126" t="inlineStr">
         <is>
           <t>Cantidad Realizada
 LA UNIÓN</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="126" t="inlineStr">
         <is>
           <t>HH Capacitación 
 LA UNIÓN</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="127" t="inlineStr">
         <is>
           <t>Cantidad Realizada
 RÍO BUENO</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="127" t="inlineStr">
         <is>
           <t>HH Capacitación 
 RÍO BUENO</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="128" t="inlineStr">
         <is>
           <t>Cantidad Realizada
 PUERTO VARAS</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N9" s="128" t="inlineStr">
         <is>
           <t>HH Capacitación 
 PUERTO VARAS</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="124" t="inlineStr">
         <is>
           <t>TOTAL
 Cantidad Realizada</t>
         </is>
       </c>
-      <c r="P9" s="12" t="inlineStr">
+      <c r="P9" s="129" t="inlineStr">
         <is>
           <t>TOTAL 
 HH Capacitación</t>
@@ -1722,44 +1872,44 @@
     </row>
     <row r="10" customFormat="1" s="52">
       <c r="A10" s="69" t="n"/>
-      <c r="B10" s="87" t="inlineStr">
+      <c r="B10" s="130" t="inlineStr">
         <is>
           <t>N° de Reuniones de Prevención de Riesgos</t>
         </is>
       </c>
-      <c r="C10" s="107" t="n"/>
-      <c r="D10" s="107" t="n"/>
-      <c r="E10" s="108" t="n"/>
-      <c r="F10" s="48" t="inlineStr">
+      <c r="C10" s="131" t="n"/>
+      <c r="D10" s="131" t="n"/>
+      <c r="E10" s="131" t="n"/>
+      <c r="F10" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G10" s="43" t="n"/>
-      <c r="H10" s="26">
+      <c r="G10" s="133" t="n"/>
+      <c r="H10" s="134">
         <f>G10*1</f>
         <v/>
       </c>
-      <c r="I10" s="25" t="n"/>
-      <c r="J10" s="26">
+      <c r="I10" s="133" t="n"/>
+      <c r="J10" s="134">
         <f>I10*1</f>
         <v/>
       </c>
-      <c r="K10" s="25" t="n"/>
-      <c r="L10" s="26">
+      <c r="K10" s="133" t="n"/>
+      <c r="L10" s="134">
         <f>K10*1</f>
         <v/>
       </c>
-      <c r="M10" s="25" t="n"/>
-      <c r="N10" s="26">
+      <c r="M10" s="133" t="n"/>
+      <c r="N10" s="134">
         <f>M10*1</f>
         <v/>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="135">
         <f>SUM(G10,I10,K10,M10)</f>
         <v/>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="136">
         <f>SUM(N10,L10,J10,H10)</f>
         <v/>
       </c>
@@ -1776,44 +1926,44 @@
     </row>
     <row r="11" customFormat="1" s="52">
       <c r="A11" s="69" t="n"/>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="130" t="inlineStr">
         <is>
           <t>N° de Charlas de Inducción (ODI)</t>
         </is>
       </c>
-      <c r="C11" s="110" t="n"/>
-      <c r="D11" s="110" t="n"/>
-      <c r="E11" s="111" t="n"/>
-      <c r="F11" s="49" t="inlineStr">
+      <c r="C11" s="131" t="n"/>
+      <c r="D11" s="131" t="n"/>
+      <c r="E11" s="131" t="n"/>
+      <c r="F11" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
         </is>
       </c>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="26">
+      <c r="G11" s="133" t="n"/>
+      <c r="H11" s="134">
         <f>G11*3</f>
         <v/>
       </c>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="26">
+      <c r="I11" s="133" t="n"/>
+      <c r="J11" s="134">
         <f>I11*3</f>
         <v/>
       </c>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="26">
+      <c r="K11" s="133" t="n"/>
+      <c r="L11" s="134">
         <f>K11*3</f>
         <v/>
       </c>
-      <c r="M11" s="25" t="n"/>
-      <c r="N11" s="26">
+      <c r="M11" s="133" t="n"/>
+      <c r="N11" s="134">
         <f>M11*3</f>
         <v/>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="135">
         <f>SUM(G11,I11,K11,M11)</f>
         <v/>
       </c>
-      <c r="P11" s="112">
+      <c r="P11" s="136">
         <f>SUM(N11,L11,J11,H11)</f>
         <v/>
       </c>
@@ -1830,44 +1980,44 @@
     </row>
     <row r="12" customFormat="1" s="52">
       <c r="A12" s="69" t="n"/>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="130" t="inlineStr">
         <is>
           <t>N° de Charlas de Inducción Visita</t>
         </is>
       </c>
-      <c r="C12" s="110" t="n"/>
-      <c r="D12" s="110" t="n"/>
-      <c r="E12" s="111" t="n"/>
-      <c r="F12" s="49" t="inlineStr">
+      <c r="C12" s="131" t="n"/>
+      <c r="D12" s="131" t="n"/>
+      <c r="E12" s="131" t="n"/>
+      <c r="F12" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
         </is>
       </c>
-      <c r="G12" s="41" t="n"/>
-      <c r="H12" s="39">
+      <c r="G12" s="133" t="n"/>
+      <c r="H12" s="134">
         <f>G12*0.25</f>
         <v/>
       </c>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="39">
+      <c r="I12" s="133" t="n"/>
+      <c r="J12" s="134">
         <f>I12*0.25</f>
         <v/>
       </c>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="26">
+      <c r="K12" s="133" t="n"/>
+      <c r="L12" s="134">
         <f>K11*0.25</f>
         <v/>
       </c>
-      <c r="M12" s="25" t="n"/>
-      <c r="N12" s="26">
+      <c r="M12" s="133" t="n"/>
+      <c r="N12" s="134">
         <f>M12*0.25</f>
         <v/>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="135">
         <f>SUM(G12,I12,K12,M12)</f>
         <v/>
       </c>
-      <c r="P12" s="112">
+      <c r="P12" s="136">
         <f>SUM(N12,L12,J12,H12)</f>
         <v/>
       </c>
@@ -1884,44 +2034,44 @@
     </row>
     <row r="13" customFormat="1" s="52">
       <c r="A13" s="69" t="n"/>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="130" t="inlineStr">
         <is>
           <t>N° de Charlas Generales (Diarias)</t>
         </is>
       </c>
-      <c r="C13" s="110" t="n"/>
-      <c r="D13" s="110" t="n"/>
-      <c r="E13" s="111" t="n"/>
-      <c r="F13" s="49" t="inlineStr">
+      <c r="C13" s="131" t="n"/>
+      <c r="D13" s="131" t="n"/>
+      <c r="E13" s="131" t="n"/>
+      <c r="F13" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="26">
+      <c r="G13" s="133" t="n"/>
+      <c r="H13" s="134">
         <f>H29*0.25</f>
         <v/>
       </c>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="26">
+      <c r="I13" s="133" t="n"/>
+      <c r="J13" s="134">
         <f>J29*0.25</f>
         <v/>
       </c>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="26">
+      <c r="K13" s="133" t="n"/>
+      <c r="L13" s="134">
         <f>L29*0.25</f>
         <v/>
       </c>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="26">
+      <c r="M13" s="133" t="n"/>
+      <c r="N13" s="134">
         <f>N29*0.25</f>
         <v/>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="135">
         <f>SUM(G13,I13,K13,M13)</f>
         <v/>
       </c>
-      <c r="P13" s="112">
+      <c r="P13" s="136">
         <f>SUM(N13,L13,J13,H13)</f>
         <v/>
       </c>
@@ -1938,44 +2088,44 @@
     </row>
     <row r="14" customFormat="1" s="52">
       <c r="A14" s="69" t="n"/>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="130" t="inlineStr">
         <is>
           <t>N° de Charlas Integrales</t>
         </is>
       </c>
-      <c r="C14" s="110" t="n"/>
-      <c r="D14" s="110" t="n"/>
-      <c r="E14" s="111" t="n"/>
-      <c r="F14" s="49" t="inlineStr">
+      <c r="C14" s="131" t="n"/>
+      <c r="D14" s="131" t="n"/>
+      <c r="E14" s="131" t="n"/>
+      <c r="F14" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="G14" s="41" t="n"/>
-      <c r="H14" s="26">
+      <c r="G14" s="133" t="n"/>
+      <c r="H14" s="134">
         <f>H30*0.5</f>
         <v/>
       </c>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="26">
+      <c r="I14" s="133" t="n"/>
+      <c r="J14" s="134">
         <f>J30*0.5</f>
         <v/>
       </c>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="26">
+      <c r="K14" s="133" t="n"/>
+      <c r="L14" s="134">
         <f>L30*0.5</f>
         <v/>
       </c>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="26">
+      <c r="M14" s="133" t="n"/>
+      <c r="N14" s="134">
         <f>N30*0.5</f>
         <v/>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="135">
         <f>SUM(G14,I14,K14,M14)</f>
         <v/>
       </c>
-      <c r="P14" s="112">
+      <c r="P14" s="136">
         <f>SUM(N14,L14,J14,H14)</f>
         <v/>
       </c>
@@ -1992,44 +2142,44 @@
     </row>
     <row r="15" customFormat="1" s="52">
       <c r="A15" s="69" t="n"/>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="130" t="inlineStr">
         <is>
           <t>Difusión de PTS</t>
         </is>
       </c>
-      <c r="C15" s="110" t="n"/>
-      <c r="D15" s="110" t="n"/>
-      <c r="E15" s="111" t="n"/>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="C15" s="131" t="n"/>
+      <c r="D15" s="131" t="n"/>
+      <c r="E15" s="131" t="n"/>
+      <c r="F15" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
         </is>
       </c>
-      <c r="G15" s="41" t="n"/>
-      <c r="H15" s="26">
+      <c r="G15" s="133" t="n"/>
+      <c r="H15" s="134">
         <f>G15*0.5</f>
         <v/>
       </c>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="26">
+      <c r="I15" s="133" t="n"/>
+      <c r="J15" s="134">
         <f>I15*0.5</f>
         <v/>
       </c>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="26">
+      <c r="K15" s="133" t="n"/>
+      <c r="L15" s="134">
         <f>K15*0.5</f>
         <v/>
       </c>
-      <c r="M15" s="25" t="n"/>
-      <c r="N15" s="26">
+      <c r="M15" s="133" t="n"/>
+      <c r="N15" s="134">
         <f>M15*0.5</f>
         <v/>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="135">
         <f>SUM(G15,I15,K15,M15)</f>
         <v/>
       </c>
-      <c r="P15" s="112">
+      <c r="P15" s="136">
         <f>SUM(N15,L15,J15,H15)</f>
         <v/>
       </c>
@@ -2046,44 +2196,44 @@
     </row>
     <row r="16" customFormat="1" s="52">
       <c r="A16" s="69" t="n"/>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="130" t="inlineStr">
         <is>
           <t>ART realizadas</t>
         </is>
       </c>
-      <c r="C16" s="110" t="n"/>
-      <c r="D16" s="110" t="n"/>
-      <c r="E16" s="111" t="n"/>
-      <c r="F16" s="49" t="inlineStr">
+      <c r="C16" s="131" t="n"/>
+      <c r="D16" s="131" t="n"/>
+      <c r="E16" s="131" t="n"/>
+      <c r="F16" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="26">
+      <c r="G16" s="133" t="n"/>
+      <c r="H16" s="134">
         <f>G16*0.25</f>
         <v/>
       </c>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="26">
+      <c r="I16" s="133" t="n"/>
+      <c r="J16" s="134">
         <f>I16*0.25</f>
         <v/>
       </c>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="26">
+      <c r="K16" s="133" t="n"/>
+      <c r="L16" s="134">
         <f>K16*0.25</f>
         <v/>
       </c>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="26">
+      <c r="M16" s="133" t="n"/>
+      <c r="N16" s="134">
         <f>M16*0.25</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="135">
         <f>SUM(G16,I16,K16,M16)</f>
         <v/>
       </c>
-      <c r="P16" s="112">
+      <c r="P16" s="136">
         <f>SUM(N16,L16,J16,H16)</f>
         <v/>
       </c>
@@ -2100,48 +2250,48 @@
     </row>
     <row r="17" customFormat="1" s="52">
       <c r="A17" s="69" t="n"/>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="130" t="inlineStr">
         <is>
           <t>N° de Inspecciones Generales a las áreas de trabajo</t>
         </is>
       </c>
-      <c r="C17" s="110" t="n"/>
-      <c r="D17" s="110" t="n"/>
-      <c r="E17" s="111" t="n"/>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="C17" s="131" t="n"/>
+      <c r="D17" s="131" t="n"/>
+      <c r="E17" s="131" t="n"/>
+      <c r="F17" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="25" t="n"/>
-      <c r="N17" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="21">
+      <c r="G17" s="133" t="n"/>
+      <c r="H17" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="133" t="n"/>
+      <c r="J17" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="133" t="n"/>
+      <c r="L17" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="133" t="n"/>
+      <c r="N17" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="135">
         <f>SUM(G17,I17,K17,M17)</f>
         <v/>
       </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="P17" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2159,48 +2309,48 @@
     </row>
     <row r="18" customFormat="1" s="52">
       <c r="A18" s="69" t="n"/>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="130" t="inlineStr">
         <is>
           <t>N° de Inspecciones a bodegas SUSPEL/RESPEL</t>
         </is>
       </c>
-      <c r="C18" s="110" t="n"/>
-      <c r="D18" s="110" t="n"/>
-      <c r="E18" s="111" t="n"/>
-      <c r="F18" s="49" t="inlineStr">
+      <c r="C18" s="131" t="n"/>
+      <c r="D18" s="131" t="n"/>
+      <c r="E18" s="131" t="n"/>
+      <c r="F18" s="132" t="inlineStr">
         <is>
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="G18" s="41" t="n"/>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="25" t="n"/>
-      <c r="N18" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="21">
+      <c r="G18" s="133" t="n"/>
+      <c r="H18" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="133" t="n"/>
+      <c r="J18" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="133" t="n"/>
+      <c r="L18" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="133" t="n"/>
+      <c r="N18" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="135">
         <f>SUM(G18,I18,K18,M18)</f>
         <v/>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="P18" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2218,48 +2368,48 @@
     </row>
     <row r="19" customFormat="1" s="52">
       <c r="A19" s="69" t="n"/>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="130" t="inlineStr">
         <is>
           <t>N° de Inspecciones a maquinarias y equipo</t>
         </is>
       </c>
-      <c r="C19" s="110" t="n"/>
-      <c r="D19" s="110" t="n"/>
-      <c r="E19" s="111" t="n"/>
-      <c r="F19" s="49" t="inlineStr">
+      <c r="C19" s="131" t="n"/>
+      <c r="D19" s="131" t="n"/>
+      <c r="E19" s="131" t="n"/>
+      <c r="F19" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G19" s="41" t="n"/>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="25" t="n"/>
-      <c r="N19" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="21">
+      <c r="G19" s="133" t="n"/>
+      <c r="H19" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="133" t="n"/>
+      <c r="J19" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="133" t="n"/>
+      <c r="L19" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="133" t="n"/>
+      <c r="N19" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="135">
         <f>SUM(G19,I19,K19,M19)</f>
         <v/>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="P19" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2277,48 +2427,48 @@
     </row>
     <row r="20" customFormat="1" s="52">
       <c r="A20" s="69" t="n"/>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="130" t="inlineStr">
         <is>
           <t>N° de Inspecciones a equipamiento de emergencia (extintores)</t>
         </is>
       </c>
-      <c r="C20" s="110" t="n"/>
-      <c r="D20" s="110" t="n"/>
-      <c r="E20" s="111" t="n"/>
-      <c r="F20" s="49" t="inlineStr">
+      <c r="C20" s="131" t="n"/>
+      <c r="D20" s="131" t="n"/>
+      <c r="E20" s="131" t="n"/>
+      <c r="F20" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G20" s="41" t="n"/>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="25" t="n"/>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="21">
+      <c r="G20" s="133" t="n"/>
+      <c r="H20" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="133" t="n"/>
+      <c r="J20" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="133" t="n"/>
+      <c r="L20" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="133" t="n"/>
+      <c r="N20" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="135">
         <f>SUM(G20,I20,K20,M20)</f>
         <v/>
       </c>
-      <c r="P20" s="22" t="inlineStr">
+      <c r="P20" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2336,48 +2486,48 @@
     </row>
     <row r="21" customFormat="1" s="52">
       <c r="A21" s="69" t="n"/>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="130" t="inlineStr">
         <is>
           <t>N° de Inspecciones a señalética de obra</t>
         </is>
       </c>
-      <c r="C21" s="110" t="n"/>
-      <c r="D21" s="110" t="n"/>
-      <c r="E21" s="111" t="n"/>
-      <c r="F21" s="49" t="inlineStr">
+      <c r="C21" s="131" t="n"/>
+      <c r="D21" s="131" t="n"/>
+      <c r="E21" s="131" t="n"/>
+      <c r="F21" s="132" t="inlineStr">
         <is>
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="G21" s="41" t="n"/>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="25" t="n"/>
-      <c r="N21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="21">
+      <c r="G21" s="133" t="n"/>
+      <c r="H21" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="133" t="n"/>
+      <c r="J21" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="133" t="n"/>
+      <c r="L21" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="133" t="n"/>
+      <c r="N21" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="135">
         <f>SUM(G21,I21,K21,M21)</f>
         <v/>
       </c>
-      <c r="P21" s="22" t="inlineStr">
+      <c r="P21" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2395,56 +2545,56 @@
     </row>
     <row r="22" customFormat="1" s="52">
       <c r="A22" s="69" t="n"/>
-      <c r="B22" s="113" t="inlineStr">
+      <c r="B22" s="130" t="inlineStr">
         <is>
           <t>Revisión de Documentación de maquinaria</t>
         </is>
       </c>
-      <c r="C22" s="110" t="n"/>
-      <c r="D22" s="110" t="n"/>
-      <c r="E22" s="114" t="n"/>
-      <c r="F22" s="49" t="inlineStr">
+      <c r="C22" s="131" t="n"/>
+      <c r="D22" s="131" t="n"/>
+      <c r="E22" s="131" t="n"/>
+      <c r="F22" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G22" s="41" t="n">
+      <c r="G22" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="27" t="n">
+      <c r="H22" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="27" t="n">
+      <c r="J22" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="25" t="n">
+      <c r="L22" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="21">
+      <c r="N22" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="135">
         <f>SUM(G22,I22,K22,M22)</f>
         <v/>
       </c>
-      <c r="P22" s="22" t="inlineStr">
+      <c r="P22" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2462,48 +2612,48 @@
     </row>
     <row r="23" customFormat="1" s="52">
       <c r="A23" s="69" t="n"/>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="130" t="inlineStr">
         <is>
           <t>Inspección de medidas de seguridad en excavaciones</t>
         </is>
       </c>
-      <c r="C23" s="110" t="n"/>
-      <c r="D23" s="110" t="n"/>
-      <c r="E23" s="111" t="n"/>
-      <c r="F23" s="49" t="inlineStr">
+      <c r="C23" s="131" t="n"/>
+      <c r="D23" s="131" t="n"/>
+      <c r="E23" s="131" t="n"/>
+      <c r="F23" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="25" t="n"/>
-      <c r="N23" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="21">
+      <c r="G23" s="133" t="n"/>
+      <c r="H23" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="133" t="n"/>
+      <c r="J23" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="133" t="n"/>
+      <c r="L23" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="133" t="n"/>
+      <c r="N23" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="135">
         <f>SUM(G23,I23,K23,M23)</f>
         <v/>
       </c>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="P23" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2521,48 +2671,48 @@
     </row>
     <row r="24" customFormat="1" s="52">
       <c r="A24" s="69" t="n"/>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B24" s="130" t="inlineStr">
         <is>
           <t>Inspección a medidas de seguridad en trabajo en altura</t>
         </is>
       </c>
-      <c r="C24" s="110" t="n"/>
-      <c r="D24" s="110" t="n"/>
-      <c r="E24" s="111" t="n"/>
-      <c r="F24" s="49" t="inlineStr">
+      <c r="C24" s="131" t="n"/>
+      <c r="D24" s="131" t="n"/>
+      <c r="E24" s="131" t="n"/>
+      <c r="F24" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="25" t="n"/>
-      <c r="N24" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="21">
+      <c r="G24" s="133" t="n"/>
+      <c r="H24" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="133" t="n"/>
+      <c r="J24" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="133" t="n"/>
+      <c r="L24" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="133" t="n"/>
+      <c r="N24" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="135">
         <f>SUM(G24,I24,K24,M24)</f>
         <v/>
       </c>
-      <c r="P24" s="22" t="inlineStr">
+      <c r="P24" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2580,48 +2730,48 @@
     </row>
     <row r="25" customFormat="1" s="52">
       <c r="A25" s="69" t="n"/>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="B25" s="130" t="inlineStr">
         <is>
           <t>Inspección de Medidas de Seguridad para trabajo en caliente.</t>
         </is>
       </c>
-      <c r="C25" s="110" t="n"/>
-      <c r="D25" s="110" t="n"/>
-      <c r="E25" s="111" t="n"/>
-      <c r="F25" s="49" t="inlineStr">
+      <c r="C25" s="131" t="n"/>
+      <c r="D25" s="131" t="n"/>
+      <c r="E25" s="131" t="n"/>
+      <c r="F25" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="25" t="n"/>
-      <c r="N25" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="21">
+      <c r="G25" s="133" t="n"/>
+      <c r="H25" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="133" t="n"/>
+      <c r="J25" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="133" t="n"/>
+      <c r="L25" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="133" t="n"/>
+      <c r="N25" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="135">
         <f>SUM(G25,I25,K25,M25)</f>
         <v/>
       </c>
-      <c r="P25" s="22" t="inlineStr">
+      <c r="P25" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2639,56 +2789,56 @@
     </row>
     <row r="26" customFormat="1" s="52">
       <c r="A26" s="69" t="n"/>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="B26" s="138" t="inlineStr">
         <is>
           <t>Inspección de Medidas de Seguridad para trabajos en espacios confinados.</t>
         </is>
       </c>
-      <c r="C26" s="110" t="n"/>
-      <c r="D26" s="110" t="n"/>
-      <c r="E26" s="111" t="n"/>
-      <c r="F26" s="50" t="inlineStr">
+      <c r="C26" s="131" t="n"/>
+      <c r="D26" s="131" t="n"/>
+      <c r="E26" s="131" t="n"/>
+      <c r="F26" s="139" t="inlineStr">
         <is>
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G26" s="44" t="n">
+      <c r="G26" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="28" t="n">
+      <c r="H26" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="28" t="n">
+      <c r="J26" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="140" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="25" t="n">
+      <c r="L26" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="21">
+      <c r="N26" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="135">
         <f>SUM(G26,I26,K26,M26)</f>
         <v/>
       </c>
-      <c r="P26" s="22" t="inlineStr">
+      <c r="P26" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2706,48 +2856,48 @@
     </row>
     <row r="27" customFormat="1" s="52">
       <c r="A27" s="69" t="n"/>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="130" t="inlineStr">
         <is>
           <t>Inspección de Herramientas Eléctricas</t>
         </is>
       </c>
-      <c r="C27" s="110" t="n"/>
-      <c r="D27" s="110" t="n"/>
-      <c r="E27" s="111" t="n"/>
-      <c r="F27" s="49" t="inlineStr">
+      <c r="C27" s="131" t="n"/>
+      <c r="D27" s="131" t="n"/>
+      <c r="E27" s="131" t="n"/>
+      <c r="F27" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="25" t="n"/>
-      <c r="N27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="21">
+      <c r="G27" s="133" t="n"/>
+      <c r="H27" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="133" t="n"/>
+      <c r="J27" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="133" t="n"/>
+      <c r="L27" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="133" t="n"/>
+      <c r="N27" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="135">
         <f>SUM(G27,I27,K27,M27)</f>
         <v/>
       </c>
-      <c r="P27" s="22" t="inlineStr">
+      <c r="P27" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2765,48 +2915,48 @@
     </row>
     <row r="28" ht="14.4" customFormat="1" customHeight="1" s="52" thickBot="1">
       <c r="A28" s="69" t="n"/>
-      <c r="B28" s="53" t="inlineStr">
+      <c r="B28" s="130" t="inlineStr">
         <is>
           <t>Inspección de Andamios</t>
         </is>
       </c>
-      <c r="C28" s="115" t="n"/>
-      <c r="D28" s="115" t="n"/>
-      <c r="E28" s="116" t="n"/>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="C28" s="131" t="n"/>
+      <c r="D28" s="131" t="n"/>
+      <c r="E28" s="131" t="n"/>
+      <c r="F28" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
         </is>
       </c>
-      <c r="G28" s="45" t="n"/>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="29" t="n"/>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="29" t="n"/>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="25" t="n"/>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="23">
+      <c r="G28" s="133" t="n"/>
+      <c r="H28" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="133" t="n"/>
+      <c r="J28" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="133" t="n"/>
+      <c r="L28" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="133" t="n"/>
+      <c r="N28" s="137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="135">
         <f>SUM(G28,I28,K28,M28)</f>
         <v/>
       </c>
-      <c r="P28" s="24" t="inlineStr">
+      <c r="P28" s="136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2824,37 +2974,25 @@
     </row>
     <row r="29" ht="14.4" customFormat="1" customHeight="1" s="52" thickBot="1">
       <c r="A29" s="69" t="n"/>
-      <c r="B29" s="52" t="n"/>
-      <c r="F29" s="51" t="inlineStr">
-        <is>
-          <t>Cantidad de Trabajadores</t>
-        </is>
-      </c>
-      <c r="G29" s="46" t="inlineStr">
-        <is>
-          <t>Cantidad de Trabajadores</t>
-        </is>
-      </c>
-      <c r="H29" s="34" t="n"/>
-      <c r="I29" s="31" t="inlineStr">
-        <is>
-          <t>Cantidad de Trabajadores ch gral</t>
-        </is>
-      </c>
-      <c r="J29" s="34" t="n"/>
-      <c r="K29" s="31" t="inlineStr">
-        <is>
-          <t>Cantidad de Trabajadores</t>
-        </is>
-      </c>
-      <c r="L29" s="34" t="n"/>
-      <c r="M29" s="31" t="inlineStr">
-        <is>
-          <t>Cantidad de Trabajadores</t>
-        </is>
-      </c>
-      <c r="N29" s="38" t="n"/>
-      <c r="O29" s="69" t="n"/>
+      <c r="B29" s="141" t="inlineStr">
+        <is>
+          <t>Cantidad de Trabajadores — Charlas Generales</t>
+        </is>
+      </c>
+      <c r="C29" s="142" t="n"/>
+      <c r="D29" s="142" t="n"/>
+      <c r="E29" s="142" t="n"/>
+      <c r="F29" s="143" t="n"/>
+      <c r="G29" s="143" t="n"/>
+      <c r="H29" s="144" t="n"/>
+      <c r="I29" s="143" t="n"/>
+      <c r="J29" s="144" t="n"/>
+      <c r="K29" s="143" t="n"/>
+      <c r="L29" s="144" t="n"/>
+      <c r="M29" s="143" t="n"/>
+      <c r="N29" s="144" t="n"/>
+      <c r="O29" s="145" t="n"/>
+      <c r="P29" s="146" t="n"/>
       <c r="Q29" s="117" t="n"/>
       <c r="R29" s="117" t="n"/>
       <c r="S29" s="117" t="n"/>
@@ -2868,32 +3006,25 @@
     </row>
     <row r="30" customFormat="1" s="52">
       <c r="A30" s="69" t="n"/>
-      <c r="B30" s="52" t="n"/>
-      <c r="G30" s="52" t="inlineStr">
-        <is>
-          <t>cantidad trab. Ch. integral</t>
-        </is>
-      </c>
-      <c r="H30" s="69" t="n"/>
-      <c r="I30" s="52" t="inlineStr">
-        <is>
-          <t>cantidad trab. Ch. integral</t>
-        </is>
-      </c>
-      <c r="J30" s="52" t="n"/>
-      <c r="K30" s="52" t="inlineStr">
-        <is>
-          <t>cantidad trab. Ch. integral</t>
-        </is>
-      </c>
-      <c r="L30" s="69" t="n"/>
-      <c r="M30" s="52" t="inlineStr">
-        <is>
-          <t>cantidad trab. Ch. integral</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n"/>
-      <c r="O30" s="69" t="n"/>
+      <c r="B30" s="141" t="inlineStr">
+        <is>
+          <t>Cantidad de Trabajadores — Charlas Integrales</t>
+        </is>
+      </c>
+      <c r="C30" s="142" t="n"/>
+      <c r="D30" s="142" t="n"/>
+      <c r="E30" s="142" t="n"/>
+      <c r="F30" s="142" t="n"/>
+      <c r="G30" s="143" t="n"/>
+      <c r="H30" s="144" t="n"/>
+      <c r="I30" s="143" t="n"/>
+      <c r="J30" s="144" t="n"/>
+      <c r="K30" s="143" t="n"/>
+      <c r="L30" s="144" t="n"/>
+      <c r="M30" s="143" t="n"/>
+      <c r="N30" s="144" t="n"/>
+      <c r="O30" s="145" t="n"/>
+      <c r="P30" s="146" t="n"/>
       <c r="Q30" s="117" t="n"/>
       <c r="R30" s="117" t="n"/>
       <c r="S30" s="117" t="n"/>
@@ -2907,29 +3038,29 @@
     </row>
     <row r="31" customFormat="1" s="52">
       <c r="A31" s="69" t="n"/>
-      <c r="B31" s="53" t="inlineStr">
+      <c r="B31" s="147" t="inlineStr">
         <is>
           <t>CPHS — Comité Paritario de Higiene y Seguridad</t>
         </is>
       </c>
-      <c r="C31" s="120" t="n"/>
-      <c r="D31" s="120" t="n"/>
-      <c r="E31" s="121" t="n"/>
-      <c r="F31" s="40" t="inlineStr">
+      <c r="C31" s="148" t="n"/>
+      <c r="D31" s="148" t="n"/>
+      <c r="E31" s="148" t="n"/>
+      <c r="F31" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="45" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="29" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="29" t="n"/>
-      <c r="L31" s="16" t="n"/>
-      <c r="M31" s="25" t="n"/>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="23" t="n"/>
-      <c r="P31" s="24" t="n"/>
+      <c r="G31" s="150" t="n"/>
+      <c r="H31" s="151" t="n"/>
+      <c r="I31" s="150" t="n"/>
+      <c r="J31" s="151" t="n"/>
+      <c r="K31" s="150" t="n"/>
+      <c r="L31" s="151" t="n"/>
+      <c r="M31" s="150" t="n"/>
+      <c r="N31" s="151" t="n"/>
+      <c r="O31" s="152" t="n"/>
+      <c r="P31" s="153" t="n"/>
       <c r="Q31" s="117" t="n"/>
       <c r="R31" s="117" t="n"/>
       <c r="S31" s="117" t="n"/>

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -89,6 +89,7 @@
     <definedName name="HRB_workers_chintegral">'Cump. Programa Prevención'!$L$30</definedName>
     <definedName name="HPV_workers_chgen">'Cump. Programa Prevención'!$N$29</definedName>
     <definedName name="HPV_workers_chintegral">'Cump. Programa Prevención'!$N$30</definedName>
+    <definedName name="report_title">'Cump. Programa Prevención'!$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -195,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -792,6 +793,76 @@
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -801,7 +872,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1200,6 +1271,12 @@
     <xf numFmtId="4" fontId="6" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1791,9 +1868,9 @@
           <t>Cumplimiento Operacional</t>
         </is>
       </c>
-      <c r="C9" s="123" t="n"/>
-      <c r="D9" s="123" t="n"/>
-      <c r="E9" s="123" t="n"/>
+      <c r="C9" s="154" t="n"/>
+      <c r="D9" s="154" t="n"/>
+      <c r="E9" s="155" t="n"/>
       <c r="F9" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve">Periodicidad de acuerdo a Plan de Prevención </t>
@@ -1877,9 +1954,9 @@
           <t>N° de Reuniones de Prevención de Riesgos</t>
         </is>
       </c>
-      <c r="C10" s="131" t="n"/>
-      <c r="D10" s="131" t="n"/>
-      <c r="E10" s="131" t="n"/>
+      <c r="C10" s="156" t="n"/>
+      <c r="D10" s="156" t="n"/>
+      <c r="E10" s="157" t="n"/>
       <c r="F10" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
@@ -1931,9 +2008,9 @@
           <t>N° de Charlas de Inducción (ODI)</t>
         </is>
       </c>
-      <c r="C11" s="131" t="n"/>
-      <c r="D11" s="131" t="n"/>
-      <c r="E11" s="131" t="n"/>
+      <c r="C11" s="156" t="n"/>
+      <c r="D11" s="156" t="n"/>
+      <c r="E11" s="157" t="n"/>
       <c r="F11" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
@@ -1985,9 +2062,9 @@
           <t>N° de Charlas de Inducción Visita</t>
         </is>
       </c>
-      <c r="C12" s="131" t="n"/>
-      <c r="D12" s="131" t="n"/>
-      <c r="E12" s="131" t="n"/>
+      <c r="C12" s="156" t="n"/>
+      <c r="D12" s="156" t="n"/>
+      <c r="E12" s="157" t="n"/>
       <c r="F12" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
@@ -2039,9 +2116,9 @@
           <t>N° de Charlas Generales (Diarias)</t>
         </is>
       </c>
-      <c r="C13" s="131" t="n"/>
-      <c r="D13" s="131" t="n"/>
-      <c r="E13" s="131" t="n"/>
+      <c r="C13" s="156" t="n"/>
+      <c r="D13" s="156" t="n"/>
+      <c r="E13" s="157" t="n"/>
       <c r="F13" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
@@ -2093,9 +2170,9 @@
           <t>N° de Charlas Integrales</t>
         </is>
       </c>
-      <c r="C14" s="131" t="n"/>
-      <c r="D14" s="131" t="n"/>
-      <c r="E14" s="131" t="n"/>
+      <c r="C14" s="156" t="n"/>
+      <c r="D14" s="156" t="n"/>
+      <c r="E14" s="157" t="n"/>
       <c r="F14" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
@@ -2147,9 +2224,9 @@
           <t>Difusión de PTS</t>
         </is>
       </c>
-      <c r="C15" s="131" t="n"/>
-      <c r="D15" s="131" t="n"/>
-      <c r="E15" s="131" t="n"/>
+      <c r="C15" s="156" t="n"/>
+      <c r="D15" s="156" t="n"/>
+      <c r="E15" s="157" t="n"/>
       <c r="F15" s="132" t="inlineStr">
         <is>
           <t>Cada vez</t>
@@ -2201,9 +2278,9 @@
           <t>ART realizadas</t>
         </is>
       </c>
-      <c r="C16" s="131" t="n"/>
-      <c r="D16" s="131" t="n"/>
-      <c r="E16" s="131" t="n"/>
+      <c r="C16" s="156" t="n"/>
+      <c r="D16" s="156" t="n"/>
+      <c r="E16" s="157" t="n"/>
       <c r="F16" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
@@ -2255,9 +2332,9 @@
           <t>N° de Inspecciones Generales a las áreas de trabajo</t>
         </is>
       </c>
-      <c r="C17" s="131" t="n"/>
-      <c r="D17" s="131" t="n"/>
-      <c r="E17" s="131" t="n"/>
+      <c r="C17" s="156" t="n"/>
+      <c r="D17" s="156" t="n"/>
+      <c r="E17" s="157" t="n"/>
       <c r="F17" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
@@ -2314,9 +2391,9 @@
           <t>N° de Inspecciones a bodegas SUSPEL/RESPEL</t>
         </is>
       </c>
-      <c r="C18" s="131" t="n"/>
-      <c r="D18" s="131" t="n"/>
-      <c r="E18" s="131" t="n"/>
+      <c r="C18" s="156" t="n"/>
+      <c r="D18" s="156" t="n"/>
+      <c r="E18" s="157" t="n"/>
       <c r="F18" s="132" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -2373,9 +2450,9 @@
           <t>N° de Inspecciones a maquinarias y equipo</t>
         </is>
       </c>
-      <c r="C19" s="131" t="n"/>
-      <c r="D19" s="131" t="n"/>
-      <c r="E19" s="131" t="n"/>
+      <c r="C19" s="156" t="n"/>
+      <c r="D19" s="156" t="n"/>
+      <c r="E19" s="157" t="n"/>
       <c r="F19" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
@@ -2432,9 +2509,9 @@
           <t>N° de Inspecciones a equipamiento de emergencia (extintores)</t>
         </is>
       </c>
-      <c r="C20" s="131" t="n"/>
-      <c r="D20" s="131" t="n"/>
-      <c r="E20" s="131" t="n"/>
+      <c r="C20" s="156" t="n"/>
+      <c r="D20" s="156" t="n"/>
+      <c r="E20" s="157" t="n"/>
       <c r="F20" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
@@ -2491,9 +2568,9 @@
           <t>N° de Inspecciones a señalética de obra</t>
         </is>
       </c>
-      <c r="C21" s="131" t="n"/>
-      <c r="D21" s="131" t="n"/>
-      <c r="E21" s="131" t="n"/>
+      <c r="C21" s="156" t="n"/>
+      <c r="D21" s="156" t="n"/>
+      <c r="E21" s="157" t="n"/>
       <c r="F21" s="132" t="inlineStr">
         <is>
           <t>Trimestral</t>
@@ -2550,9 +2627,9 @@
           <t>Revisión de Documentación de maquinaria</t>
         </is>
       </c>
-      <c r="C22" s="131" t="n"/>
-      <c r="D22" s="131" t="n"/>
-      <c r="E22" s="131" t="n"/>
+      <c r="C22" s="156" t="n"/>
+      <c r="D22" s="156" t="n"/>
+      <c r="E22" s="157" t="n"/>
       <c r="F22" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
@@ -2617,9 +2694,9 @@
           <t>Inspección de medidas de seguridad en excavaciones</t>
         </is>
       </c>
-      <c r="C23" s="131" t="n"/>
-      <c r="D23" s="131" t="n"/>
-      <c r="E23" s="131" t="n"/>
+      <c r="C23" s="156" t="n"/>
+      <c r="D23" s="156" t="n"/>
+      <c r="E23" s="157" t="n"/>
       <c r="F23" s="132" t="inlineStr">
         <is>
           <t>Mensual</t>
@@ -2676,9 +2753,9 @@
           <t>Inspección a medidas de seguridad en trabajo en altura</t>
         </is>
       </c>
-      <c r="C24" s="131" t="n"/>
-      <c r="D24" s="131" t="n"/>
-      <c r="E24" s="131" t="n"/>
+      <c r="C24" s="156" t="n"/>
+      <c r="D24" s="156" t="n"/>
+      <c r="E24" s="157" t="n"/>
       <c r="F24" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
@@ -2735,9 +2812,9 @@
           <t>Inspección de Medidas de Seguridad para trabajo en caliente.</t>
         </is>
       </c>
-      <c r="C25" s="131" t="n"/>
-      <c r="D25" s="131" t="n"/>
-      <c r="E25" s="131" t="n"/>
+      <c r="C25" s="156" t="n"/>
+      <c r="D25" s="156" t="n"/>
+      <c r="E25" s="157" t="n"/>
       <c r="F25" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
@@ -2794,9 +2871,9 @@
           <t>Inspección de Medidas de Seguridad para trabajos en espacios confinados.</t>
         </is>
       </c>
-      <c r="C26" s="131" t="n"/>
-      <c r="D26" s="131" t="n"/>
-      <c r="E26" s="131" t="n"/>
+      <c r="C26" s="156" t="n"/>
+      <c r="D26" s="156" t="n"/>
+      <c r="E26" s="157" t="n"/>
       <c r="F26" s="139" t="inlineStr">
         <is>
           <t>Diaria</t>
@@ -2861,9 +2938,9 @@
           <t>Inspección de Herramientas Eléctricas</t>
         </is>
       </c>
-      <c r="C27" s="131" t="n"/>
-      <c r="D27" s="131" t="n"/>
-      <c r="E27" s="131" t="n"/>
+      <c r="C27" s="156" t="n"/>
+      <c r="D27" s="156" t="n"/>
+      <c r="E27" s="157" t="n"/>
       <c r="F27" s="132" t="inlineStr">
         <is>
           <t>Semanal</t>
@@ -2920,9 +2997,9 @@
           <t>Inspección de Andamios</t>
         </is>
       </c>
-      <c r="C28" s="131" t="n"/>
-      <c r="D28" s="131" t="n"/>
-      <c r="E28" s="131" t="n"/>
+      <c r="C28" s="156" t="n"/>
+      <c r="D28" s="156" t="n"/>
+      <c r="E28" s="157" t="n"/>
       <c r="F28" s="132" t="inlineStr">
         <is>
           <t>Diaria</t>
@@ -2979,9 +3056,9 @@
           <t>Cantidad de Trabajadores — Charlas Generales</t>
         </is>
       </c>
-      <c r="C29" s="142" t="n"/>
-      <c r="D29" s="142" t="n"/>
-      <c r="E29" s="142" t="n"/>
+      <c r="C29" s="156" t="n"/>
+      <c r="D29" s="156" t="n"/>
+      <c r="E29" s="157" t="n"/>
       <c r="F29" s="143" t="n"/>
       <c r="G29" s="143" t="n"/>
       <c r="H29" s="144" t="n"/>
@@ -3011,9 +3088,9 @@
           <t>Cantidad de Trabajadores — Charlas Integrales</t>
         </is>
       </c>
-      <c r="C30" s="142" t="n"/>
-      <c r="D30" s="142" t="n"/>
-      <c r="E30" s="142" t="n"/>
+      <c r="C30" s="156" t="n"/>
+      <c r="D30" s="156" t="n"/>
+      <c r="E30" s="157" t="n"/>
       <c r="F30" s="142" t="n"/>
       <c r="G30" s="143" t="n"/>
       <c r="H30" s="144" t="n"/>
@@ -3043,9 +3120,9 @@
           <t>CPHS — Comité Paritario de Higiene y Seguridad</t>
         </is>
       </c>
-      <c r="C31" s="148" t="n"/>
-      <c r="D31" s="148" t="n"/>
-      <c r="E31" s="148" t="n"/>
+      <c r="C31" s="158" t="n"/>
+      <c r="D31" s="158" t="n"/>
+      <c r="E31" s="159" t="n"/>
       <c r="F31" s="149" t="inlineStr">
         <is>
           <t>—</t>

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -90,6 +90,7 @@
     <definedName name="HPV_workers_chgen">'Cump. Programa Prevención'!$N$29</definedName>
     <definedName name="HPV_workers_chintegral">'Cump. Programa Prevención'!$N$30</definedName>
     <definedName name="report_title">'Cump. Programa Prevención'!$E$2</definedName>
+    <definedName name="HPV_workers_difpts">'Cump. Programa Prevención'!$N$15</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2248,9 +2249,8 @@
         <v/>
       </c>
       <c r="M15" s="133" t="n"/>
-      <c r="N15" s="134">
-        <f>M15*0.5</f>
-        <v/>
+      <c r="N15" s="134" t="n">
+        <v>0</v>
       </c>
       <c r="O15" s="135">
         <f>SUM(G15,I15,K15,M15)</f>

--- a/data/templates/RESUMEN_template_v1.xlsx
+++ b/data/templates/RESUMEN_template_v1.xlsx
@@ -77,10 +77,6 @@
     <definedName name="HLU_andamios_count">'Cump. Programa Prevención'!$I$28</definedName>
     <definedName name="HRB_andamios_count">'Cump. Programa Prevención'!$K$28</definedName>
     <definedName name="HPV_andamios_count">'Cump. Programa Prevención'!$M$28</definedName>
-    <definedName name="HLL_chps_count">'Cump. Programa Prevención'!$G$31</definedName>
-    <definedName name="HLU_chps_count">'Cump. Programa Prevención'!$I$31</definedName>
-    <definedName name="HRB_chps_count">'Cump. Programa Prevención'!$K$31</definedName>
-    <definedName name="HPV_chps_count">'Cump. Programa Prevención'!$M$31</definedName>
     <definedName name="HLL_workers_chgen">'Cump. Programa Prevención'!$H$29</definedName>
     <definedName name="HLL_workers_chintegral">'Cump. Programa Prevención'!$H$30</definedName>
     <definedName name="HLU_workers_chgen">'Cump. Programa Prevención'!$J$29</definedName>
@@ -91,6 +87,14 @@
     <definedName name="HPV_workers_chintegral">'Cump. Programa Prevención'!$N$30</definedName>
     <definedName name="report_title">'Cump. Programa Prevención'!$E$2</definedName>
     <definedName name="HPV_workers_difpts">'Cump. Programa Prevención'!$N$15</definedName>
+    <definedName name="HLL_revdocmaq_count">'Cump. Programa Prevención'!$G$22</definedName>
+    <definedName name="HLL_espacios_count">'Cump. Programa Prevención'!$G$26</definedName>
+    <definedName name="HLU_revdocmaq_count">'Cump. Programa Prevención'!$I$22</definedName>
+    <definedName name="HLU_espacios_count">'Cump. Programa Prevención'!$I$26</definedName>
+    <definedName name="HRB_revdocmaq_count">'Cump. Programa Prevención'!$K$22</definedName>
+    <definedName name="HRB_espacios_count">'Cump. Programa Prevención'!$K$26</definedName>
+    <definedName name="HPV_revdocmaq_count">'Cump. Programa Prevención'!$M$22</definedName>
+    <definedName name="HPV_espacios_count">'Cump. Programa Prevención'!$M$26</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
